--- a/legacy/previous_app/assets/ui_v2/audio_prompts.xlsx
+++ b/legacy/previous_app/assets/ui_v2/audio_prompts.xlsx
@@ -276,7 +276,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pod warstwa popiółu przy studni widać znak wypalony w kamieniu: otwarta dłoń nad plomieniem. To nie jest ostrzezenie przed klatwa. To znak strażnikow.</t>
+          <t>Pod warstwą popiółu przy studni widać znak wypalony w kamieniu: otwarta dłoń nad płomieniem. To nie jest ostrzeżenie przed klątwą. To znak strażników.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -390,7 +390,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Konfesjonal stoi nietkniety, choc wszystko wokol niego jest czarne. Z jego wnetrza pada jedno pytanie: wyznajcie, co spalilo ten dom.</t>
+          <t>Konfesjonal stoi nietknięty, choć wszystko wokół niego jest czarne. Z jego wnętrza pada jedno pytanie: wyznajcie, co spaliło ten dom.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Popiol przy oltarzu unosi sie w ksztalt spalonego duchownego. Pastoral uderza o kamien, a czerwony zar rozlewa sie po posadzce.</t>
+          <t>Popiół przy ołtarzu unosi się w kształt spalonego duchownego. Pastoral uderza o kamień, a czerwony żar rozlewa się po posadzce.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Deacon rozpada sie na popiol, lecz oltarz rozblyskuje czerwienia. Cos pod kamieniem sciaga go z powrotem. Nie da sie go zniszczyc, dopoki oltarz plonie.</t>
+          <t>Deacon rozpada się na popiół, lecz ołtarz rozbłyskuje czerwienią. Coś pod kamieniem ściąga go z powrotem. Nie da się go zniszczyć, dopóki ołtarz płonie.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Czerwony zar pod oltarzem peka i gasnie. Zostaje zimne swiatlo, a ze Spalonego Diakona odpada sila, ktora trzymala go przy zyciu.</t>
+          <t>Czerwony żar pod ołtarzem pęka i gaśnie. Zostaje zimne światło, a ze Spalonego Diakona odpada siła, która trzymała go przy życiu.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Spalony Diakon rozpada sie bez powrotu. Jego ostatni szept nie oskarza Miry. Powtarza tylko jedno slowo: milczenie.</t>
+          <t>Spalony Diakon rozpada się bez powrotu. Jego ostatni szept nie oskarza Miry. Powtarza tylko jedno słowo: milczenie.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>W krypcie pod oltarzem znajdujecie medalion Serai i fragment pieczeci z herbem Vale'a. Relikwiarz nie zostal spalony. Zostal wyniesiony.</t>
+          <t>W krypcie pod ołtarzem znajdujecie medalion Serai i fragment pieczęci z herbem Vale'a. Relikwiarz nie został spalony. Został wyniesiony.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tovin wychodzi z zamknietej komory blady, ale zywy. Pokazuje worek falszywego popiółu i przysiega, ze widzial ludzi kasztelana przy kaplicy.</t>
+          <t>Tovin wychodzi z zamkniętej komory blady, ale żywy. Pokazuje worek fałszywego popiółu i przysięga, że widział ludzi kasztelana przy kaplicy.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Za workami maki znajduje sie waski trakt prowadzacy w stronę ruin. Pozwala ominac strażnikow na glownej drodze.</t>
+          <t>Za workami mąki znajduje się wąski trakt prowadzący w stronę ruin. Pozwala ominąć strażników na głównej drodze.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>W popielnym wspomnieniu widzicie kaplice jeszcze przed pozarem. Odran Vale stoi przy oltarzu. Jeden z jego ludzi trzyma relikwiarz, drugi wyciera krew z noza.</t>
+          <t>W popielnym wspomnieniu widzicie kaplicę jeszcze przed pożarem. Odran Vale stoi przy ołtarzu. Jeden z jego ludzi trzyma relikwiarz, drugi wyciera krew z noża.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Gdy relikwiarz wraca na miejsce, plomienie w sarkofagach gasna jeden po drugim. Nad ranem Brindleford wciaz pachnie popiółem, ale z kominow unosi sie zwykly dym.</t>
+          <t>Gdy relikwiarz wraca na miejsce, płomienie w sarkofagach gasną jeden po drugim. Nad ranem Brindleford wciąż pachnie popiółem, ale z kominów unosi się zwykły dym.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Relikwiarz znika za brama krypty. Popielni straznicy nie ruszaja za nim od razu. Daja Brindleford czas, by zrozumialo, ze wyrok zostal tylko odlozony.</t>
+          <t>Relikwiarz znika za bramą krypty. Popielni strażnicy nie ruszają za nim od razu. Daje Brindleford czas, by zrozumiało, że wyrok został tylko odłożony.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Zapetlona muzyka walki z bossem w spalonej kaplicy: niskie choralne drony, suche trzaski zaru, powolna perkusja rytualna, napiecie bez zagluszania rozmow przy stole.</t>
+          <t>Zapętlona muzyka walki z bossem w spalonej kaplicy: niskie choralne drony, suche trzaski żaru, powolna perkusja rytualna, napięcie bez zagłuszania rozmów przy stole.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Odran odcina rozmówe: najpierw porzadek, potem pytania. Patrol staje blizej studni.</t>
+          <t>Odran odcina rozmowę: najpierw porządek, potem pytania. Patrol staje bliżej studni.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Odran bierze pytanie za prowokacje. Jego ludzie zapamietuja twarze druzyny.</t>
+          <t>Odran bierze pytanie za prowokację. Jego ludzie zapamiętują twarze drużyny.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Odran odpowiada za szybko: relikwiarz splonal, Mira uciekla, a kaplica jest niebezpieczna. Slowo 'splonal' nie pasuje do zamknietego relikwiarza z brazu.</t>
+          <t>Odran odpowiada za szybko: relikwiarz spłonął, Mira uciekła, a kaplica jest niebezpieczna. Słowo 'spłonął' nie pasuje do zamkniętego relikwiarza z brązu.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Elna sciska chuste w dłońiach. Patrzy najpierw na patrol, potem na droge do starego młyna. Widac, ze wie wiecej, niz chce powiedziec przy ludziach Odrana.</t>
+          <t>Elna ściska chustę w dłoniach. Patrzy najpierw na patrol, potem na drogę do starego młyna. Widać, że wie więcej, niż chce powiedzieć przy ludziach Odrana.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Elna szepcze, ze jej brat Tovin zniknal po tym, jak zobaczyl ludzi Odrana niosacych cos ciezkiego w stronę młyna. Jesli go znajdziecie, moze wskazac trakt do ruin.</t>
+          <t>Elna szepcze, że jej brat Tovin zniknął po tym, jak zobaczył ludzi Odrana niosących coś ciężkiego w stronę młyna. Jeśli go znajdziecie, może wskazać trakt do ruin.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Widzisz, ze Elna nie boi sie Miry. Boi sie, ze patrol uslyszy imie Tovina.</t>
+          <t>Widzisz, że Elna nie boi się Miry. Boi się, że patrol usłyszy imię Tovina.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Jej wzrok co chwile ucieka ku drodze do młyna.</t>
+          <t>Jej wzrok co chwilę ucieka ku drodze do młyna.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Strach Elny miesza sie ze zmeczeniem. Nie da sie odczytac nic pewnego.</t>
+          <t>Strach Elny miesza się ze zmęczeniem. Nie da się odczytać nic pewnego.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tomas, młynarski parobek, udaje, ze poprawia rzemien przy wiadrze. Na butach ma make, a pod nia ciemny popiół nie z rynku.</t>
+          <t>Tomas, młynarski parobek, udaje, że poprawia rzemień przy wiadrze. Na butach ma mąkę, a pod nią ciemny popiół nie z rynku.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tomas przyznaje, ze widzial ludzi Odrana przy starym mlynie. Jeden niosl metalowa skrzynie, a drugi rozsypywal popiół z worka, jakby chcial zrobic falszywy trop.</t>
+          <t>Tomas przyznaje, że widział ludzi Odrana przy starym młynie. Jeden niósł metalową skrzynię, a drugi rozsypywał popiół z worka, jakby chciał zrobić fałszywy trop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tomas wskazuje droge do młyna. Mówi tylko: 'Tam zaczal sie ten popiół, nie przy kaplicy.'</t>
+          <t>Tomas wskazuje drogę do młyna. Mówi tylko: 'Tam zaczął się ten popiół, nie przy kaplicy.'</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tomas spuszcza głowę. 'Ja tylko nosze worki. Nic nie widzialem.'</t>
+          <t>Tomas spuszcza głowę. 'Ja tylko noszę worki. Nic nie widziałem.'</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Mara trzyma koszyk przykryty plocienna szmata. Czuc spod niej ostre ziola i spirytus. Nie ufa obcym, ale jej wzrok mieknie, gdy widzi rannych.</t>
+          <t>Mara trzyma koszyk przykryty płócienną szmatą. Czuć spod niej ostre zioła i spirytus. Nie ufa obcym, ale jej wzrok mięknie, gdy widzi rannych.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Mara uznaje, ze naprawde probujecie pomoc wiosce. Wsuwa wam piec malych zawiniatek z zielem.</t>
+          <t>Mara uznaje, że naprawdę próbujecie pomóc wiosce. Wsuwa wam pięć małych zawiniątek z zielem.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Mara nie odda zapasow za darmo, ale moze sprzedac do pieciu porcji po 1 gp za sztuke.</t>
+          <t>Mara nie odda zapasów za darmo, ale może sprzedać do pięciu porcji po 1 gp za sztukę.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Mara zaciska dłoń na koszyku. 'Nie mam nic dla ludzi, ktorzy moga sciagnac patrol na moj prog.'</t>
+          <t>Mara zaciska dłoń na koszyku. 'Nie mam nic dla ludzi, którzy mogą ściągnąć patrol na mój próg.'</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Mara uznaje pytanie za probe wymuszenia i odchodzi pod sciane karczmy.</t>
+          <t>Mara uznaje pytanie za próbę wymuszenia i odchodzi pod ścianę karczmy.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Brann opowiada, ze popiół spadl z nieba, studnia spiewala, a Mira ma oczy jak noc. Po chwili sam gubi kolejnosc zdarzen.</t>
+          <t>Brann opowiada, że popiół spadł z nieba, studnia śpiewała, a Mira ma oczy jak noc. Po chwili sam gubi kolejność zdarzeń.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Nila szepcze, że nie widziała Miry przy ogniu. Widziała za to człowieka Odrana, który przed świtem wsypal cos czarnego do wiadra przy studni, a potem zgubil kawałek czerwonego sznura.</t>
+          <t>Nila szepcze, że nie widziała Miry przy ogniu. Widziała za to człowieka Odrana, który przed świtem wsypał coś czarnego do wiadra przy studni, a potem zgubił kawałek czerwonego sznura.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Nila nabiera odwagi. Mówi, ze przy studni stal strażnik z czerwonym sznurem przy rękojeści, a popiół wysypal sie z worka, nie z nieba. Wskazuje miejsce, gdzie trzeba szukać śladu.</t>
+          <t>Nila nabiera odwagi. Mówi, że przy studni stał strażnik z czerwonym sznurem przy rękojeści, a popiół wysypał się z worka, nie z nieba. Wskazuje miejsce, gdzie trzeba szukać śladu.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Nila nie poda nazwiska, ale pokazuje na studnie. Powtarza tylko: "To nie byla pani Mira. To byl pan z czerwonym sznurem."</t>
+          <t>Nila nie poda nazwiska, ale pokazuje na studnię. Powtarza tylko: "To nie była pani Mira. To był pan z czerwonym sznurem."</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Dziewczynka chowa kamyki do kieszeni i milknie. Jej wzrok mowi jednak jasno: dopoki patrol stoi tak blisko, nie będzie mowic.</t>
+          <t>Dziewczynka chowa kamyki do kieszeni i milknie. Jej wzrok mówi jednak jasno: dopóki patrol stoi tak blisko, nie będzie mówić.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Nila zaczyna plakac. Jeden ze strażnikow natychmiast patrzy w wasza stronę i zapamietuje twarze.</t>
+          <t>Nila zaczyna płakać. Jeden ze strażników natychmiast patrzy w waszą stronę i zapamiętuje twarze.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bren siedzi pod sciana z mokra chusta na ustach. Kaszle czarnym pylem, ale to nie wyglada jak zwykly dym po pożarze. Mara co chwile patrzy w jego stronę, pilnowana wzrokiem patrolu.</t>
+          <t>Bren siedzi pod ścianą z mokrą chustą na ustach. Kaszle czarnym pylem, ale to nie wygląda jak zwykły dym po pożarze. Mara co chwilę patrzy w jego stronę, pilnowana wzrokiem patrolu.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Udaje sie oczyscic mu gardlo i odroznic pyl od sadzy. Bren lapie oddech i mowi, ze popiół przyniesiono w workach od strony młyna, zanim kaplica zaczela dymic. Prosi też, żeby szukać czystej wody w południowo-wschodniej części miasta, przy odpływie głównej drogi.</t>
+          <t>Udaje się oczyścić mu gardło i odróżnić pył od sadzy. Bren łapie oddech i mówi, że popiół przyniesiono w workach od strony młyna, zanim kaplica zaczęła dymić. Prosi też, żeby szukać czystej wody w południowo-wschodniej części miasta, przy odpływie głównej drogi.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bren uspokaja oddech na tyle, by wyszeptac: "To nie byl popiół z kaplicy. Pachnial mokrym zbozem... mlynem." Po chwili wskazuje drżącą ręką południowo-wschodnią część miasta i prosi o czystą wodę z odpływu przy głównej drodze.</t>
+          <t>Bren uspokaja oddech na tyle, by wyszeptać: "To nie był popiół z kaplicy. Pachniał mokrym zbożem... młynem." Po chwili wskazuje drżącą ręką południowo-wschodnią część miasta i prosi o czystą wodę z odpływu przy głównej drodze.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Nie pogarszasz jego stanu, ale Bren nie jest w stanie mowic. Mara szepcze, ze bez ciszy, ziela i czystej wody niewiele da sie zrobic. Wskazuje południowo-wschodnią część miasta, gdzie przy głównej drodze może być jeszcze niezabrudzony odpływ.</t>
+          <t>Nie pogarszasz jego stanu, ale Bren nie jest w stanie mówić. Mara szepcze, że bez ciszy, ziela i czystej wody niewiele da się zrobić. Wskazuje południowo-wschodnią część miasta, gdzie przy głównej drodze może być jeszcze niezabrudzony odpływ.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bren dostaje ataku kaszlu, a tlum cofa się nerwowo. Patrol wykorzystuje zamieszanie, by uciszyc swiadkow, ale Mara zdąży szepnąć, że czystej wody trzeba szukać przy odpływie w południowo-wschodniej części miasta.</t>
+          <t>Bren dostaje ataku kaszlu, a tłum cofa się nerwowo. Patrol wykorzystuje zamieszanie, by uciszyć świadków, ale Mara zdąży szepnąć, że czystej wody trzeba szukać przy odpływie w południowo-wschodniej części miasta.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Mara podaje Brenowi krople gorzkiego naparu. Nie jest to cud, ale mezczyzna przestaje dlawic sie pylem. Zielarka kiwa wam glowa z ostrozna wdziecznoscia.</t>
+          <t>Mara podaje Brenowi krople gorzkiego naparu. Nie jest to cud, ale mężczyzna przestaje dławić się pylem. Zielarka kiwa wam głową z ostrożną wdzięcznością.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Patrol Odrana stoi między drużyną a mieszkańcami. Celem nie jest upokorzenie strażnikow, tylko stworzenie chwili, w ktorej świadkowie będą mogli mówić bez strachu. Możecie odwołać sie do porządku, do dobra wioski albo do prawa do zadawania pytan.</t>
+          <t>Patrol Odrana stoi między drużyną a mieszkańcami. Celem nie jest upokorzenie strażników, tylko stworzenie chwili, w której świadkowie będą mogli mówić bez strachu. Możecie odwołać się do porządku, do dobra wioski albo do prawa do zadawania pytań.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Patrol cofa się o krok. Mieszkańcy widzą, ze można mówić przybyszom prawde.</t>
+          <t>Patrol cofa się o krok. Mieszkańcy widzą, że można mówić przybyszom prawdę.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Patrol zbija rozmówę krótkimi rozkazami i mieszkańcy nadal milczą.</t>
+          <t>Patrol zbija rozmowę krótkimi rozkazami i mieszkańcy nadal milczą.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Patrol odpuszcza na tyle, by kilka osób mogło odpowiedziec szeptem.</t>
+          <t>Patrol odpuszcza na tyle, by kilka osób mogło odpowiedzieć szeptem.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Patrol uznaje rozmówę za próbę podburzania tłumu. Odran będzie bardziej czujny.</t>
+          <t>Patrol uznaje rozmowę za próbę podburzania tłumu. Odran będzie bardziej czujny.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Echo układa się w sensowny trop: ktoś przy studni powtarzal słowa przysięgi, zanim podłożono fałszywy popiół.</t>
+          <t>Echo układa się w sensowny trop: ktoś przy studni powtarzał słowa przysięgi, zanim podłożono fałszywy popiół.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Echo rozbija slowa na szmer. Na razie studnia daje tylko niepokoj, nie dowod.</t>
+          <t>Echo rozbija słowa na szmer. Na razie studnia daje tylko niepokój, nie dowód.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Słyszycie pełną fraze: "Popiół ma wskazać Mire, lecz dłoń Vale'a trzyma worek." To mocny trop przeciw wersji Odrana.</t>
+          <t>Słyszycie pełną frazę: "Popiół ma wskazać Mirę, lecz dłoń Vale'a trzyma worek." To mocny trop przeciw wersji Odrana.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Rynek nie odpowiada. Odran wykorzystuje cisze, by przypomniec ludziom, kto tu wydaje rozkazy.</t>
+          <t>Rynek nie odpowiada. Odran wykorzystuje ciszę, by przypomnieć ludziom, kto tu wydaje rozkazy.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Przemówa trafia w sedno. Mieszkańcy zaczynają poprawiać wersje patrolu na głos, a Odran musi udawać, że pozwala na pytania.</t>
+          <t>Przemowa trafia w sedno. Mieszkańcy zaczynają poprawiać wersję patrolu na głos, a Odran musi udawać, że pozwala na pytania.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Nie ma owacji, ale strach pęka. Swiadkowie będą bardziej rozmówni, jeśli podejdziecie do nich osobno.</t>
+          <t>Nie ma owacji, ale strach pęka. Świadkowie będą bardziej rozmówni, jeśli podejdziecie do nich osobno.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Słowa odbijaja sie od zamknietych okiennic. Tłum wciąż chce pomoc, lecz nie teraz i nie przy patrolu.</t>
+          <t>Słowa odbijają się od zamkniętych okiennic. Tłum wciąż chce pomóc, lecz nie teraz i nie przy patrolu.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Odran przejmuje wasze słowa i obraca je przeciwko wam. Strażnicy stają bliżej, a ludzie spuszczaja wzrok.</t>
+          <t>Odran przejmuje wasze słowa i obraca je przeciwko wam. Strażnicy stają bliżej, a ludzie spuszczają wzrok.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Przy progu kaplicy popiol lezy warstwami. To nie wyglada jak zwykly pozar: ktos przeszedl tedy po fakcie, niosac cos ciezkiego i probujac zasypac slad.</t>
+          <t>Przy progu kaplicy popiół leży warstwami. To nie wygląda jak zwykły pożar: ktoś przeszedł tędy po fakcie, niosąc coś ciężkiego i próbując zasypać ślad.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Slady przy progu ukladaja sie w trase ludzi niosacych ciezki relikwiarz, nie w ucieczke przed ogniem.</t>
+          <t>Ślady przy progu układają się w trasę ludzi niosących ciężki relikwiarz, nie w ucieczkę przed ogniem.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Popiol miesza tropy i nie daje pewnego kierunku.</t>
+          <t>Popiół miesza tropy i nie daje pewnego kierunku.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Odczytujesz dwie warstwy: najpierw wyniesiono relikwiarz, potem rozsypano popiol, zeby wygladalo na rytual Miry.</t>
+          <t>Odczytujesz dwie warstwy: najpierw wyniesiono relikwiarz, potem rozsypano popiół, żeby wyglądało na rytuał Miry.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Slady przy progu ukladaja sie w trase ludzi niosacych ciezki relikwiarz, nie w ucieczke przed ogniem.</t>
+          <t>Ślady przy progu układają się w trasę ludzi niosących ciężki relikwiarz, nie w ucieczkę przed ogniem.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Popiol miesza tropy i nie daje pewnego kierunku.</t>
+          <t>Popiół miesza tropy i nie daje pewnego kierunku.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Zacieracie czesc drobnych sladow, zanim rozumiecie ich uklad.</t>
+          <t>Zacieracie część drobnych śladów, zanim rozumiecie ich układ.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Mira stoi w popielnym kregu, ale nie wyglada jak ktos, kto rzuca klatwe. Trzyma rytual w ryzach resztkami glosu. 'Jesli przerwiecie krag mieczem, wspomnienie rozpadnie sie razem z prawda.'</t>
+          <t>Mira stoi w popielnym kręgu, ale nie wygląda jak ktoś, kto rzuca klątwę. Trzyma rytuał w ryzach resztkami głosu. 'Jeśli przerwiecie krąg mieczem, wspomnienie rozpadnie się razem z prawdą.'</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Mira tlumaczy, ze popiol pamieta dotyk sprawcy. Kreg nie wskrzesza zmarlych; utrzymuje moment kradziezy relikwiarza, zanim duchy straza go rozerwa.</t>
+          <t>Mira tłumaczy, że popiół pamięta dotyk sprawcy. Krąg nie wskrzesza zmarłych; utrzymuje moment kradzieży relikwiarza, zanim duchy straży go rozerwą.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Mira mowi, ze Odran potrzebowal relikwiarza, zeby przejac stara przysiege Serai. Jesli udowodnicie kradziez, duch krypty moze jeszcze posluchac zywych.</t>
+          <t>Mira mówi, że Odran potrzebował relikwiarza, żeby przejąć starą przysięgę Serai. Jeśli udowodnicie kradzież, duch krypty może jeszcze posłuchać żywych.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Dostrajasz szept do kregu. W popiele widac Odranowska pieczec na sakwie jednego z ludzi.</t>
+          <t>Dostrajasz szept do kręgu. W popiele widać odranowską pieczęć na sakwie jednego z ludzi.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Kreg przestaje drzec. Mira ma czas dopowiedziec, gdzie szukac wejscia do krypty.</t>
+          <t>Krąg przestaje drżeć. Mira ma czas dopowiedzieć, gdzie szukać wejścia do krypty.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Popiol wiruje zbyt szybko. Mira utrzymuje rytual sama, ale traci czas i sile.</t>
+          <t>Popiół wiruje zbyt szybko. Mira utrzymuje rytuał sama, ale traci czas i siłę.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Popielny krag nie atakuje sam z siebie. To zapis wspomnienia: mozna go odczytac jak rytual, albo zniszczyc i stracic dowod.</t>
+          <t>Popielny krąg nie atakuje sam z siebie. To zapis wspomnienia: można go odczytać jak rytuał, albo zniszczyć i stracić dowód.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Rytual Miry nie jest klatwa; stabilizuje wspomnienie, zanim duchy je rozerwa.</t>
+          <t>Rytuał Miry nie jest klątwą; stabilizuje wspomnienie, zanim duchy je rozerwą.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Popielne symbole drza zbyt szybko, by odczytac ich logike.</t>
+          <t>Popielne symbole drżą zbyt szybko, by odczytać ich logikę.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Rozumiesz rytual i jego granice: Mira utrzymuje prawde, a nie klatwe. Mozecie uzyc kregu jako dowodu w krypcie.</t>
+          <t>Rozumiesz rytuał i jego granice: Mira utrzymuje prawdę, a nie klątwę. Możecie użyć kręgu jako dowodu w krypcie.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Rytual Miry nie jest klatwa; stabilizuje wspomnienie, zanim duchy je rozerwa.</t>
+          <t>Rytuał Miry nie jest klątwą; stabilizuje wspomnienie, zanim duchy je rozerwą.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Popielne symbole drza zbyt szybko, by odczytac ich logike.</t>
+          <t>Popielne symbole drżą zbyt szybko, by odczytać ich logikę.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Dotykasz zlego znaku i wspomnienie szarpie sie, jakby chcialo wyrwac sie z kregu.</t>
+          <t>Dotykasz złego znaku i wspomnienie szarpie się, jakby chciało wyrwać się z kręgu.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Serai jest bardziej wspomnieniem niz osoba. Jej glos brzmi spod kamienia: 'Przysiega nie chroni relikwiarza. Relikwiarz przypomina, komu przysiega sluzy.'</t>
+          <t>Serai jest bardziej wspomnieniem niż osoba. Jej głos brzmi spod kamienia: 'Przysięga nie chroni relikwiarza. Relikwiarz przypomina, komu przysięga służy.'</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Serai odpowiada, ze trzeba nazwac prawde przy relikwiarzu: kto go wyniosl, kto zostal obwiniony i czy wioska ma dalej skladac przysiege strachowi.</t>
+          <t>Serai odpowiada, że trzeba nazwać prawdę przy relikwiarzu: kto go wyniósł, kto został obwiniony i czy wioska ma dalej składać przysięgę strachowi.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Krypta cichnie. Serai przyjmuje dowody i pozwala wam mowic przy relikwiarzu bez gniewu duchow.</t>
+          <t>Krypta cichnie. Serai przyjmuje dowody i pozwala wam mówić przy relikwiarzu bez gniewu duchów.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Odran nie udaje juz troski. 'Wioska potrzebuje pana, nie martwej przysiegi. Wezcie zloto i pozwolcie mi wyprowadzic relikwiarz.'</t>
+          <t>Odran nie udaje już troski. 'Wioska potrzebuje pana, nie martwej przysięgi. Weźcie złoto i pozwolcie mi wyprowadzić relikwiarz.'</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Odran cofa sie, gdy nawet jego ludzie slysza, ze oferta jest przyznaniem winy.</t>
+          <t>Odran cofa się, gdy nawet jego ludzie słyszą, że oferta jest przyznaniem winy.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Odran traci pewnosc. Jego oferta zostaje wypowiedziana na glos i staje sie dowodem.</t>
+          <t>Odran traci pewność. Jego oferta zostaje wypowiedziana na głos i staje się dowodem.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Odran usmiecha sie chlodno. 'Bez dowodu to tylko gniew przybyszow.'</t>
+          <t>Odran uśmiecha się chłodno. 'Bez dowodu to tylko gniew przybyszów.'</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Kamienne slowa przysiegi sa starte. Jesli wypowiecie je poprawnie, Serai odzyska glos; jesli zrobicie z nich tylko formule, krypta odpowie echem bez sensu.</t>
+          <t>Kamienne słowa przysięgi są starte. Jeśli wypowiecie je poprawnie, Serai odzyska głos; jeśli zrobicie z nich tylko formułę, krypta odpowie echem bez sensu.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Slowa przysiegi porzadkuja echo krypty i wzmacniaja argument za ocaleniem wioski.</t>
+          <t>Słowa przysięgi porządkują echo krypty i wzmacniają argument za ocaleniem wioski.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Echo krypty rozbija formule, zanim da sie ja domknac.</t>
+          <t>Echo krypty rozbija formułę, zanim da się ją domknąć.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Wypowiadasz slowa tak, jak byly skladane: jako obietnice wobec ludzi, nie wobec wladzy. Serai odzyskuje pelny glos.</t>
+          <t>Wypowiadasz słowa tak, jak były składane: jako obietnice wobec ludzi, nie wobec władzy. Serai odzyskuje pełny głos.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Slowa przysiegi porzadkuja echo krypty i wzmacniaja argument za ocaleniem wioski.</t>
+          <t>Słowa przysięgi porządkują echo krypty i wzmacniają argument za ocaleniem wioski.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Echo krypty rozbija formule, zanim da sie ja domknac.</t>
+          <t>Echo krypty rozbija formułę, zanim da się ją domknąć.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Krypta odpowiada gniewem dawnych straznikow, ktorzy slysza w slowach tylko pusty rytual.</t>
+          <t>Krypta odpowiada gniewem dawnych strażników, którzy słyszą w słowach tylko pusty rytuał.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Tovin siedzi zwiazany za workami maki. Jest blady, ale przytomny; zanim krzyknie z ulgi, przykłada palec do ust i nasluchuje krokow straznikow.</t>
+          <t>Tovin siedzi związany za workami mąki. Jest blady, ale przytomny; zanim krzyknie z ulgi, przykłada palec do ust i nasłuchuje kroków strażników.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Tovin mowi, ze ludzie Odrana przyniesli worki z czarnym pylem jeszcze przed pozarem kaplicy. Jeden z nich kazal mu milczec, bo "Mira ma pasowac do historii".</t>
+          <t>Tovin mówi, że ludzie Odrana przynieśli worki z czarnym pyłem jeszcze przed pożarem kaplicy. Jeden z nich kazał mu milczeć, bo "Mira ma pasować do historii".</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Tovin przestaje drzec. Wskazuje ciche przejscie za belka i obiecuje zeznac przeciw Odranowi, jesli przezyje noc.</t>
+          <t>Tovin przestaje drżeć. Wskazuje ciche przejście za belką i obiecuje zeznać przeciw Odranowi, jeśli przeżyje noc.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Tovin bierze oddech i pokazuje, ktoredy najlatwiej wyprowadzic go z mlyna bez alarmu.</t>
+          <t>Tovin bierze oddech i pokazuje, którędy najłatwiej wyprowadzić go z młyna bez alarmu.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Tovin kiwa glowa, ale strach miesza mu slowa. Na razie trzeba go po prostu uwolnic.</t>
+          <t>Tovin kiwa głową, ale strach miesza mu słowa. Na razie trzeba go po prostu uwolnić.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Tovin wpada w panike i szarpie wiezy. Gdzies za sciana ktos przestaje chodzic i zaczyna sluchac.</t>
+          <t>Tovin wpada w panikę i szarpie więzy. Gdzieś za ścianą ktoś przestaje chodzić i zaczyna słuchać.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Belka klinuje boczne przejscie. Jesli pusci cicho, Tovin bedzie mial droge ucieczki; jesli narobicie halasu, straz przy mlynie szybciej zrozumie, co robicie.</t>
+          <t>Belka klinuje boczne przejście. Jeśli puści cicho, Tovin będzie miał drogę ucieczki; jeśli narobicie hałasu, straż przy młynie szybciej zrozumie, co robicie.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Belka puszcza z trzaskiem i droga do Tovina robi sie szersza.</t>
+          <t>Belka puszcza z trzaskiem i droga do Tovina robi się szersza.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Belka ani drgnie, a mechanizm mlyna zaczyna pracowac glosniej.</t>
+          <t>Belka ani drgnie, a mechanizm młyna zaczyna pracować głośniej.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Belka schodzi z cichym skrzypnieciem. Tovin moze przejsc, a straznicy nie od razu orientuja sie w zmianie.</t>
+          <t>Belka schodzi z cichym skrzypnięciem. Tovin może przejść, a strażnicy nie od razu orientują się w zmianie.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Belka puszcza z trzaskiem i droga do Tovina robi sie szersza.</t>
+          <t>Belka puszcza z trzaskiem i droga do Tovina robi się szersza.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Belka ani drgnie, a mechanizm mlyna zaczyna pracowac glosniej.</t>
+          <t>Belka ani drgnie, a mechanizm młyna zaczyna pracować głośniej.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Belka uderza o kolo mlyna. Huk niesie sie po calym budynku.</t>
+          <t>Belka uderza o koło młyna. Huk niesie się po całym budynku.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Ciemne smyczki, metaliczne uderzenia i presja finałowej decyzji przy czerwonej bramie Odrana.</t>
+          <t>Ciemne smyczki, metaliczne uderzenia i presją finałowej decyzji przy czerwonej bramie Odrana.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>`player_ui/content/bandit_cave.json` -&gt; `briefing_intro`</t>
+          <t/>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>spokojne tempo, wyrazne pauzy po stawce misji i po opisie ukrytych przejsc. Narastajace napiecie bez patosu.</t>
+          <t>spokojne tempo, wyraźne pauzy po stawce misji i po opisie ukrytych przejść. Narastające napięcie bez patosu.</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2. Lektor: szczekanie psa jako podpowiedz</t>
+          <t>2. Lektor: szczekanie psa jako podpowiedź</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>`scenario_flows/bandit_cave.json` -&gt; event `cave_intro`</t>
+          <t/>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>krotka, praktyczna wskazowka. Pauza przed ostatnim zdaniem.</t>
+          <t>krótka, praktyczna wskazówka. Pauza przed ostatnim zdaniem.</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Odlegle szczekniecie psa w kamiennym tunelu, bardzo cichy poglos jaskini, bez jumpscare i bez dominowania nad narracja.</t>
+          <t>Odległe szczeknięcie psa w kamiennym tunelu, bardzo cichy pogłos jaskini, bez jumpscare i bez dominowania nad narracją.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>3. Muzyka: petla napiecia jaskini</t>
+          <t>3. Muzyka: pętla napięcia jaskini</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>`assets/ui_v2/bandit_cave/manifest.json` -&gt; `music.default`</t>
+          <t/>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Stworz petle muzyczna do Player UI, scenariusz Bandit Cave. Dlugosc 45-60 sekund, seamless loop. Klimat: skradanie w jaskini bandytow, kontrabanda, niepewnosc przed walka. Instrumentarium: niskie drony, pojedyncze uderzenia bebna ramowego, szorstkie smyczki lub lira korbowa bardzo subtelnie. Tempo wolne, bez melodii wpadajacej w ucho, bez epickiego refrenu. Mix ma zostawiac miejsce na dialog lektora i dzwieki UI.</t>
+          <t>Stwórz pętlę muzyczną do Player UI, scenariusz Bandit Cave. Długość 45-60 sekund, seamless loop. Klimat: skradanie w jaskini bandytów, kontrabanda, niepewność przed walką. Instrumentarium: niskie drony, pojedyncze uderzenia bębna ramowego, szorstkie smyczki lub lira korbowa bardzo subtelnie. Tempo wolne, bez melodii wpadającej w ucho, bez epickiego refrenu. Mix ma zostawiać miejsce na dialog lektora i dźwięki UI.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>4. Ambience: wejscie do jaskini</t>
+          <t>4. Ambience: wejście do jaskini</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>`assets/ui_v2/bandit_cave/manifest.json` -&gt; `music.cave_entrance`</t>
+          <t/>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Stworz ambientowa petle tla dla Player UI, mapa Cave Entrance w scenariuszu Bandit Cave. Dlugosc 45-60 sekund, seamless loop. Brzmienie: krople wody, cichy przeciag w kamiennym tunelu, odlegle skrzypniecia drewna, pojedyncze stlumione odglosy bandytow daleko w glebi. Bez wyraznej muzyki, bez glosnych jumpscare, bez rozpoznawalnych slow. Ma dzialac pod narracja i kliknieciami UI.</t>
+          <t>Stwórz ambientową pętlę tła dla Player UI, mapa Cave Entrance w scenariuszu Bandit Cave. Długość 45-60 sekund, seamless loop. Brzmienie: krople wody, cichy przeciąg w kamiennym tunelu, odległe skrzypnięcia drewna, pojedyncze stłumione odgłosy bandytów daleko w głębi. Bez wyraźnej muzyki, bez głośnych jumpscare, bez rozpoznawalnych słów. Ma działać pod narracją i kliknięciami UI.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>`images/placeholders/default_choice.svg`, przyciski wyboru w `player_ui/static/app.js`</t>
+          <t/>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Wygeneruj krotki dzwiek UI dla Player UI, scenariusz Bandit Cave: potwierdzenie wyboru opcji. Czas: 0.25-0.5 sekundy. Brzmienie: cichy klik drewnianego znacznika na stole plus lekki metaliczny akcent, jak moneta lub nit przy skorzanym pasku. Ma byc czytelny, ale nie agresywny. Bez melodii.</t>
+          <t>Wygeneruj krótki dźwięk UI dla Player UI, scenariusz Bandit Cave: potwierdzenie wyboru opcji. Czas: 0.25-0.5 sekundy. Brzmienie: cichy klik drewnianego znacznika na stole plus lekki metaliczny akcent, jak moneta lub nit przy skórzanym pasku. Ma być czytelny, ale nie agresywny. Bez melodii.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>panel `Aktywna inicjatywa`, assety aktorow i przeciwnikow</t>
+          <t/>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Wygeneruj krotki dzwiek UI dla Player UI oznaczajacy zmiane aktywnego aktora w inicjatywie. Czas: 0.35-0.7 sekundy. Klimat Bandit Cave: szybki niski puls, przesuniecie pionka po drewnie, delikatny poglos jaskini. Dzwiek ma informowac, ze teraz czyjas tura jest aktywna. Bez alarmu i bez triumfalnej melodii.</t>
+          <t>Wygeneruj krótki dźwięk UI dla Player UI oznaczający zmianę aktywnego aktora w inicjatywie. Czas: 0.35-0.7 sekundy. Klimat Bandit Cave: szybki niski puls, przesunięcie pionka po drewnie, delikatny pogłos jaskini. Dźwięk ma informować, że teraz czyjaś tura jest aktywna. Bez alarmu i bez triumfalnej melodii.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>7. Start: wejscie do jaskini</t>
+          <t>7. Start: wejście do jaskini</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -11783,18 +11783,18 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>`scenario_flows/bandit_cave.json` -&gt; `cave_intro`</t>
+          <t/>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>opis lokacji, cicho i napiecie. Pierwsze zdanie wolniej, ostatnie bardziej informacyjnie.</t>
+          <t>opis lokacji, cicho i napięcie. Pierwsze zdanie wolniej, ostatnie bardziej informacyjnie.</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
           <t>Stoisz przed wejściem do jaskini bandytów. Kamień przy progu jest wilgotny, a ślady prowadzą głębiej, w stronę nierównego tunelu.
-Z ciemności dochodzi ruch, jakby ktoś przesuwał skrzynie albo broń po ziemi. Po chwili ciszę przecina szczekanie psa.
+Z ciemności dochodzi ruch, jakby ktoś przesuwał skrzynię albo broń po ziemi. Po chwili ciszę przecina szczekanie psa.
 Przejście nie jest puste. Drużyna ma kilka oddechów, zanim kryjówka zorientuje się, że ktoś nadchodzi.</t>
         </is>
       </c>
@@ -11822,7 +11822,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>8. Odkrycie sekretnego przejscia</t>
+          <t>8. Odkrycie sekretnego przejścia</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>`scenario_flows/bandit_cave.json` -&gt; `secret_discovered`</t>
+          <t/>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>ostrozna satysfakcja, ale bez triumfu. Dobra pauza przed wzmianka o skarbcu.</t>
+          <t>ostrożną satysfakcja, ale bez triumfu. Dobra pauza przed wzmianka o skarbcu.</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>`scenario_flows/bandit_cave.json` -&gt; `cave_cleared`</t>
+          <t/>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>10. Wejscie do skarbca</t>
+          <t>10. Wejście do skarbca</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>`scenario_flows/bandit_cave.json` -&gt; `treasure_intro`</t>
+          <t/>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>skupiony opis pomieszczenia, ostrzegawcza pauza przed pulapka.</t>
+          <t>skupiony opis pomieszczenia, ostrzegawcza pauza przed pułapką.</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>11. Wejscie do dokow</t>
+          <t>11. Wejście do doków</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12017,18 +12017,18 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>`scenario_flows/bandit_cave.json` -&gt; `docks_intro`</t>
+          <t/>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>final scenariusza coraz blizej, ale nadal opisowo.</t>
+          <t>final scenariusza coraz bliżej, ale nadal opisowo.</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
           <t>Tunel opada niżej i otwiera się na podziemne doki. Woda odbija słabe światło, a przy nabrzeżu kołysze się łódź przygotowana do odpłynięcia.
-Na deskach leżą liny, skrzynie i resztki załadunku. Jeśli przemytnicy utrzymają ten pomost, kontrabanda zniknie razem z dowodami.
+Na deskach leżą liny, skrzynię i resztki załadunku. Jeśli przemytnicy utrzymają ten pomost, kontrabanda zniknie razem z dowodami.
 To tutaj trzeba przerwać szlak.</t>
         </is>
       </c>
@@ -12076,12 +12076,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>`scenario_flows/bandit_cave.json` -&gt; `docks_cleared`</t>
+          <t/>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>finalna ulga, bez fanfar. Ostatnie zdanie wyraznie domyka cel.</t>
+          <t>finalna ulga, bez fanfar. Ostatnie zdanie wyraźnie domyka cel.</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>`scenario_flows/bandit_cave.json` -&gt; `escape_by_ship`, `player_ui/content/bandit_cave.json` -&gt; `result_summary`</t>
+          <t/>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>`player_ui/templates/index.html`</t>
+          <t/>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>jasny komunikat startowy, bez teatralnego przeciagania.</t>
+          <t>jasny komunikat startowy, bez teatralnego przeciągania.</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -12250,12 +12250,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>`player_ui/templates/index.html` -&gt; `Zbierz drużynę`</t>
+          <t/>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>funkcjonalne tempo, wyrazny zakres liczby bohaterow.</t>
+          <t>funkcjonalne tempo, wyraźny zakres liczby bohaterów.</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>`player_ui/content/bandit_cave.json` -&gt; `briefing_title`, `stakes`</t>
+          <t/>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>konkretnie, z naciskiem na stawke.</t>
+          <t>konkretnie, z naciskiem na stawkę.</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>`player_ui/templates/index.html` i `player_ui/static/app.js`</t>
+          <t/>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>neutralnie, bez napiecia.</t>
+          <t>neutralnie, bez napięcia.</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>`player_ui/templates/index.html` -&gt; `Błąd połączenia`</t>
+          <t/>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Bardzo krotki, niski i nienachalny dzwiek ostrzegawczy UI, bez alarmu i bez melodii.</t>
+          <t>Bardzo krótki, niski i nienachalny dźwięk ostrzegawczy UI, bez alarmu i bez melodii.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>19. Scenariusz zakonczony</t>
+          <t>19. Scenariusz zakończony</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>`player_ui/static/app.js` -&gt; fallback result</t>
+          <t/>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>`images/actions/stride.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX dla ikony akcji "Ruch / Stride" w Player UI, Bandit Cave. Czas: 0.4-0.8 sekundy. Brzmienie: dwa szybkie kroki po wilgotnym kamieniu, lekki poglos jaskini. Dzwiek ma byc subtelny i pasowac do klikniecia akcji, bez glosu.</t>
+          <t>Wygeneruj SFX dla ikony akcji "Ruch / Stride" w Player UI, Bandit Cave. Czas: 0.4-0.8 sekundy. Brzmienie: dwa szybkie kroki po wilgotnym kamieniu, lekki pogłos jaskini. Dźwięk ma być subtelny i pasować do kliknięcia akcji, bez głosu.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>`images/actions/strike.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX dla ikony akcji "Strike / Attack" w Player UI, Bandit Cave. Czas: 0.35-0.7 sekundy. Brzmienie: krotkie swisniecie ostrza i stlumione uderzenie w skore lub drewno, bez krzyku i bez gore. Ma byc czytelny jako akcja bojowa.</t>
+          <t>Wygeneruj SFX dla ikony akcji "Strike / Attack" w Player UI, Bandit Cave. Czas: 0.35-0.7 sekundy. Brzmienie: krótkie świstnięcie ostrza i stłumione uderzenie w skórę lub drewno, bez krzyku i bez gore. Ma być czytelny jako akcja bojowa.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>`images/actions/interact.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX dla ikony "Interact" w Player UI, Bandit Cave. Czas: 0.35-0.7 sekundy. Brzmienie: dlon dotykajaca starej skrzyni, drobne skrzypniecie zawiasu, lekki metaliczny detal. Bez glosu.</t>
+          <t>Wygeneruj SFX dla ikony "Interact" w Player UI, Bandit Cave. Czas: 0.35-0.7 sekundy. Brzmienie: dłoń dotykająca starej skrzyni, drobne skrzypnięcie zawiasu, lekki metaliczny detal. Bez głosu.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>`images/actions/seek.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX dla ikony "Seek" w Player UI, Bandit Cave. Czas: 0.5-0.9 sekundy. Brzmienie: ciche przesuniecie kamyka, skupiony niski ton, delikatne odkrycie szczegolu. Ma sugerowac przeszukiwanie jaskini, nie magie.</t>
+          <t>Wygeneruj SFX dla ikony "Seek" w Player UI, Bandit Cave. Czas: 0.5-0.9 sekundy. Brzmienie: ciche przesunięcie kamyka, skupiony niski ton, delikatne odkrycie szczegółu. Ma sugerować przeszukiwanie jaskini, nie magię.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>`images/actions/end_turn.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX dla ikony "End Turn" w Player UI. Czas: 0.35-0.6 sekundy. Brzmienie: pionek odstawiany na plansze i krotki niski klik. Neutralne, bez poczucia porazki ani sukcesu.</t>
+          <t>Wygeneruj SFX dla ikony "End Turn" w Player UI. Czas: 0.35-0.6 sekundy. Brzmienie: pionek odstawiany na planszę i krótki niski klik. Neutralne, bez poczucia porażki ani sukcesu.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>`images/actions/defend.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX dla ikony "Raise Shield / Defend" w Player UI, Bandit Cave. Czas: 0.45-0.8 sekundy. Brzmienie: tarcza podnoszona na przedramieniu, skora napieta na pasku, delikatny metaliczny rezonans. Ma byc obronne, zwarte, bez dlugiego wybrzmienia.</t>
+          <t>Wygeneruj SFX dla ikony "Raise Shield / Defend" w Player UI, Bandit Cave. Czas: 0.45-0.8 sekundy. Brzmienie: tarcza podnoszona na przedramieniu, skóra napięta na pasku, delikatny metaliczny rezonans. Ma być obronne, zwarte, bez długiego wybrzmienia.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>`images/enemies/bandit.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Wygeneruj krotki earcon dla pojawienia sie lub tury przeciwnika "Bandit" w Player UI, Bandit Cave. Czas: 0.8-1.2 sekundy. Brzmienie: krok po kamieniu, skorzany pas, krotki nieartykulowany pomruk daleko w poglosie. Bez slow, bez przesady.</t>
+          <t>Wygeneruj krótki earcon dla pojawienia się lub tury przeciwnika "Bandit" w Player UI, Bandit Cave. Czas: 0.8-1.2 sekundy. Brzmienie: krok po kamieniu, skórzany pas, krótki nieartykułowany pomruk daleko w pogłosie. Bez słów, bez przesady.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>`images/enemies/bandit_sharpshot.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Wygeneruj earcon dla przeciwnika "Bandit Sharpshot" w Player UI, Bandit Cave. Czas: 0.8-1.3 sekundy. Brzmienie: napinana cieciwa lub kusza, delikatny klik mechanizmu, cichy oddech w jaskini. Bez wystrzalu jako glosnego efektu, bo to tylko identyfikacja przeciwnika.</t>
+          <t>Wygeneruj earcon dla przeciwnika "Bandit Sharpshot" w Player UI, Bandit Cave. Czas: 0.8-1.3 sekundy. Brzmienie: napinana cięciwa lub kusza, delikatny klik mechanizmu, cichy oddech w jaskini. Bez wystrzału jako głośnego efektu, bo to tylko identyfikacja przeciwnika.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>`images/enemies/guard_dog.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -13003,7 +13003,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Wygeneruj earcon dla psa strazniczego w Player UI, Bandit Cave. Czas: 0.8-1.2 sekundy. Brzmienie: niski warkot i szybkie pazury na kamieniu, z poglosem jaskini. Bez glosnego szczekania, aby nie meczylo przy powtarzaniu tur.</t>
+          <t>Wygeneruj earcon dla psa strażniczego w Player UI, Bandit Cave. Czas: 0.8-1.2 sekundy. Brzmienie: niski warkot i szybkie pazury na kamieniu, z pogłosem jaskini. Bez głośnego szczekania, aby nie męczyło przy powtarzaniu tur.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>`images/characters/narrator.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Wygeneruj krotki earcon dla komunikatu narratora w Player UI, Bandit Cave. Czas: 0.5-0.9 sekundy. Brzmienie: niski, cieply ton jak otwarcie ksiegi plus delikatny poglos kamiennej sali. Ma sygnalizowac, ze zaraz pojawi sie tekst mistrza gry.</t>
+          <t>Wygeneruj krótki earcon dla komunikatu narratora w Player UI, Bandit Cave. Czas: 0.5-0.9 sekundy. Brzmienie: niski, ciepły ton jak otwarcie księgi plus delikatny pogłos kamiennej sali. Ma sygnalizować, że zaraz pojawi się tekst mistrza gry.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>`images/spells/acid_splash.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX dla czaru "Acid Splash" w Player UI, Bandit Cave. Czas: 0.8-1.4 sekundy. Brzmienie: kwas syczy na kamieniu, lepki rozprysk, lekki magiczny impuls na poczatku. Bez krzyku, bez dlugiego ogona.</t>
+          <t>Wygeneruj SFX dla czaru "Acid Splash" w Player UI, Bandit Cave. Czas: 0.8-1.4 sekundy. Brzmienie: kwas syczy na kamieniu, lepki rozprysk, lekki magiczny impuls na początku. Bez krzyku, bez długiego ogona.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>`images/spells/electric_arc.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX dla czaru "Electric Arc" w Player UI, Bandit Cave. Czas: 0.7-1.2 sekundy. Brzmienie: krotki luk elektryczny odbijajacy sie od wilgotnego kamienia, ostre trzaski, ale bez bardzo wysokiej glosnosci. Ma byc dynamiczne i czytelne.</t>
+          <t>Wygeneruj SFX dla czaru "Electric Arc" w Player UI, Bandit Cave. Czas: 0.7-1.2 sekundy. Brzmienie: krótki łuk elektryczny odbijający się od wilgotnego kamienia, ostre trzaski, ale bez bardzo wysokiej głośności. Ma być dynamiczne i czytelne.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>`images/spells/heal.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX dla czaru "Heal" w Player UI, Bandit Cave. Czas: 0.9-1.5 sekundy. Brzmienie: cieple swiatlo, delikatny choralny oddech bez slow, subtelny blysk. Ma odrozniac sie od ciemnego ambience jaskini, ale nie byc cukierkowe.</t>
+          <t>Wygeneruj SFX dla czaru "Heal" w Player UI, Bandit Cave. Czas: 0.9-1.5 sekundy. Brzmienie: ciepłe światło, delikatny choralny oddech bez słów, subtelny błysk. Ma odróżniać się od ciemnego ambience jaskini, ale nie być cukierkowe.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>`images/spells/magic_missile.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX dla czaru "Magic Missile" w Player UI, Bandit Cave. Czas: 0.8-1.3 sekundy. Brzmienie: trzy szybkie magiczne pociski, kazdy z krotkim swistem i lekkim uderzeniem energii. Bez eksplozji, bez sci-fi laserow.</t>
+          <t>Wygeneruj SFX dla czaru "Magic Missile" w Player UI, Bandit Cave. Czas: 0.8-1.3 sekundy. Brzmienie: trzy szybkie magiczne pociski, każdy z krótkim świstem i lekkim uderzeniem energii. Bez eksplozji, bez sci-fi laserów.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>`images/spells/cantrip.svg`, `images/spells/focus.svg`, `images/spells/rank_1.svg`</t>
+          <t/>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Wygeneruj neutralny SFX dla ogolnej ikony czaru w Player UI, Bandit Cave. Czas: 0.45-0.8 sekundy. Brzmienie: delikatne magiczne rozswietlenie, krotki niski ton i lekki szelest pergaminu. Ma pasowac do cantrip, focus i czaru rangi 1, bez sugerowania konkretnego zywiolu.</t>
+          <t>Wygeneruj neutralny SFX dla ogólnej ikony czaru w Player UI, Bandit Cave. Czas: 0.45-0.8 sekundy. Brzmienie: delikatne magiczne rozświetlenie, krótki niski ton i lekki szelest pergaminu. Ma pasować do cantrip, focus i czaru rangi 1, bez sugerowania konkretnego żywiołu.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>`scenarios/bandit_cave_treasure_room.json`</t>
+          <t/>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Stworz seamless loop ambience dla mapy Treasure Room w Player UI, Bandit Cave. Dlugosc 35-50 sekund. Brzmienie: mniejsza kamienna komora, skrzynie, stary papier, delikatne pobrzmiewanie monet, prawie nieslyszalny mechanizm pulapki. Bez muzyki, bez glosow, tlo pod narracje.</t>
+          <t>Stwórz seamless loop ambience dla mapy Treasure Room w Player UI, Bandit Cave. Długość 35-50 sekund. Brzmienie: mniejsza kamienna komora, skrzynie, stary papier, delikatne pobrzmiewanie monet, prawie niesłyszalny mechanizm pułapki. Bez muzyki, bez głosów, tło pod narrację.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>`scenarios/bandit_cave_smuggler_docks.json`</t>
+          <t/>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Stworz seamless loop ambience dla mapy Smuggler Docks w Player UI, Bandit Cave. Dlugosc 45-60 sekund. Brzmienie: podziemna przystan, woda o pale, skrzypiace deski, liny, odlegly przeciag w duzej grocie. Niski poziom glosnosci, bez melodii i bez rozpoznawalnych slow.</t>
+          <t>Stwórz seamless loop ambience dla mapy Smuggler Docks w Player UI, Bandit Cave. Długość 45-60 sekund. Brzmienie: podziemna przystań, woda o pale, skrzypiące deski, liny, odległy przeciąg w dużej grocie. Niski poziom głośności, bez melodii i bez rozpoznawalnych słów.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>37. Pulapka: plyta naciskowa</t>
+          <t>37. Pułapka: płyta naciskowa</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>`scenarios/bandit_cave_treasure_room.json` -&gt; `Skarbcowa płyta naciskowa`</t>
+          <t/>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX pulapki do Player UI, Bandit Cave: skarbcowa plyta naciskowa. Czas: 1.0-1.6 sekundy. Brzmienie: kamienna plyta opada o kilka milimetrow, ukryta igla wyskakuje, metaliczny alarmowy trzask. Bez krzyku postaci, bez gore.</t>
+          <t>Wygeneruj SFX pułapki do Player UI, Bandit Cave: skarbcowa płyta naciskowa. Czas: 1.0-1.6 sekundy. Brzmienie: kamienna płyta opada o kilka milimetrów, ukryta igła wyskakuje, metaliczny alarmowy trzask. Bez krzyku postaci, bez gore.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>38. Pulapka: iglowa skrytka</t>
+          <t>38. Pułapka: igłowa skrytka</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>`scenarios/bandit_cave_treasure_room.json` -&gt; `Igłowa pułapka skrytki`</t>
+          <t/>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX dla ukrytej iglowej pulapki w skrytce, Player UI, Bandit Cave. Czas: 0.8-1.3 sekundy. Brzmienie: szybki sprzeg mechanizmu, syk malej igly, krotki metaliczny trzask alarmu w kamiennej komorze. Bez glosu i bez krwi.</t>
+          <t>Wygeneruj SFX dla ukrytej igłowej pułapki w skrytce, Player UI, Bandit Cave. Czas: 0.8-1.3 sekundy. Brzmienie: szybki sprzęg mechanizmu, syk małej igły, krótki metaliczny trzask alarmu w kamiennej komorze. Bez głosu i bez krwi.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>`scenarios/bandit_cave_treasure_room.json` -&gt; `description_on_reveal`</t>
+          <t/>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX odkrycia ukrytej skrytki w Player UI, Bandit Cave. Czas: 0.8-1.4 sekundy. Brzmienie: falszywa deska odsuwa sie, cichy szelest papierow i monet, delikatny ton odkrycia. Bez fanfary, bardziej skradankowo niz zwyciesko.</t>
+          <t>Wygeneruj SFX odkrycia ukrytej skrytki w Player UI, Bandit Cave. Czas: 0.8-1.4 sekundy. Brzmienie: fałszywa deska odsuwa się, cichy szelest papierów i monet, delikatny ton odkrycia. Bez fanfary, bardziej skradankowo niż zwycięsko.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>40. Statek przemytnikow</t>
+          <t>40. Statek przemytników</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>`scenarios/bandit_cave_smuggler_docks.json` -&gt; exit `Smuggler Ship`</t>
+          <t/>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Wygeneruj SFX interakcji ze statkiem przemytnikow w Player UI, Bandit Cave. Czas: 1.0-1.8 sekundy. Brzmienie: lina odpinana od pala, drewno lodzi skrzypi, woda chlupie przy burcie. Ma sugerowac gotowosc do ucieczki z podziemnych dokow.</t>
+          <t>Wygeneruj SFX interakcji ze statkiem przemytników w Player UI, Bandit Cave. Czas: 1.0-1.8 sekundy. Brzmienie: lina odpinana od pala, drewno łodzi skrzypi, woda chlupie przy burcie. Ma sugerować gotowość do ucieczki z podziemnych doków.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>41. Marek "Lina" Voss - NPC zwiazany przemytnik</t>
+          <t>41. Marek "Lina" Voss - NPC związany przemytnik</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -13734,12 +13734,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>`scenarios/bandit_cave_smuggler_docks.json`, `src/GameObjects/NPC/bound_smuggler_npc.py`</t>
+          <t/>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>szybka zaczepka z dokow. Pierwsze slowo ciszej, potem konkretny haczyk.</t>
+          <t>szybka zaczepka z doków. Pierwsze słowo ciszej, potem konkretny haczyk.</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>prosi o pomoc, ale probuje od razu negocjowac.</t>
+          <t>prosi o pomoc, ale próbuje od razu negocjować.</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Marek - kim jestes?</t>
+          <t>Marek - kim jesteś?</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>zaczyna ostroznie, potem na moment pojawia sie zawodowa duma.</t>
+          <t>zaczyna ostrożnie, potem na moment pojawia się zawodowa duma.</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>krotko, targuje sie i testuje reakcje druzyny.</t>
+          <t>krótko, targuje się i testuje reakcje drużyny.</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Marek - wskazuje skrytke</t>
+          <t>Marek - wskazuje skrytkę</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>szybciej, praktycznie, jak instrukcja przekazana pod presja.</t>
+          <t>szybciej, praktycznie, jak instrukcja przekazana pod presją.</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>podejrzliwie, bez podnoszenia glosu.</t>
+          <t>podejrzliwie, bez podnoszenia głosu.</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>spiete, nerwowa odwaga, szybka pauza przed ostatnim zdaniem.</t>
+          <t>spięte, nerwowa odwaga, szybka pauza przed ostatnim zdaniem.</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>ciszej i ostrzej, jak ktos sklada fakty.</t>
+          <t>ciszej i ostrzej, jak ktoś składa fakty.</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Marek - zlapany na klamstwie</t>
+          <t>Marek - złapany na kłamstwie</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>niechetnie przyznaje prawde, natychmiast szuka nowego ukladu.</t>
+          <t>niechętnie przyznaje prawdę, natychmiast szuka nowego układu.</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -14243,7 +14243,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Marek - uwolniony i wspolpracuje</t>
+          <t>Marek - uwolniony i współpracuje</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>ostroznie, kontroluje kazde slowo.</t>
+          <t>ostrożnie, kontroluje każde słowo.</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Marek - probuje rzucic sie do lodzi</t>
+          <t>Marek - próbuje rzucić się do łodzi</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>bardzo krotko, nagly ruch. SFX osobno po slowach.</t>
+          <t>bardzo krótko, nagły ruch. SFX osobno po słowach.</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Szarpniecie luzowanej liny, szybki krok po mokrym drewnie, chlupot wody przy burcie, bez krzyku.</t>
+          <t>Szarpnięcie luzowanej liny, szybki krok po mokrym drewnie, chlupot wody przy burcie, bez krzyku.</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Marek - zatrzymany grozba</t>
+          <t>Marek - zatrzymany groźbą</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14384,7 +14384,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>szybko, przestraszony, ale stara sie nie stracic twarzy.</t>
+          <t>szybko, przestraszony, ale stara się nie stracić twarzy.</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -14417,7 +14417,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Marek - zatrzymany zmylka</t>
+          <t>Marek - zatrzymany zmyłką</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Marek - luzem przy lodzi</t>
+          <t>Marek - luzem przy łodzi</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>zdyszany, odzyskuje przewage, ale jeszcze nie triumfuje.</t>
+          <t>zdyszany, odzyskuje przewagę, ale jeszcze nie triumfuje.</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Marek - skrytka juz wskazana</t>
+          <t>Marek - skrytka już wskazana</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>krotkie przypomnienie po ponownym pytaniu o skrytke.</t>
+          <t>krótkie przypomnienie po ponownym pytaniu o skrytkę.</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>krotki stan NPC po odwiązaniu; bardziej narrator/komunikat sytuacyjny niz nowa kwestia.</t>
+          <t>krótki stan NPC po odwiązaniu; bardziej narrator/komunikat sytuacyjny niż nowa kwestia.</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Marek - proba ponownego odwiązania</t>
+          <t>Marek - próba ponownego odwiązania</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>bardzo krotki komunikat stanu, bez dramatyzowania.</t>
+          <t>bardzo krótki komunikat stanu, bez dramatyzowania.</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>opcjonalny, krotki komunikat UI po wybraniu zakonczenia rozmowy.</t>
+          <t>opcjonalny, krótki komunikat UI po wybraniu zakończenia rozmowy.</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>43. Status: audio wlaczone/wylaczone</t>
+          <t>43. Status: audio włączone/wyłączone</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>`Audio on`, `Audio off`, `Muted`</t>
+          <t/>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>neutralnie, maksymalnie krotko.</t>
+          <t>neutralnie, maksymalnie krótko.</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>`Cele`, `Cele pojawią się po starcie scenariusza`</t>
+          <t/>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -14959,12 +14959,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>`Brak aktywnej inicjatywy`</t>
+          <t/>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>neutralnie, bez efektow.</t>
+          <t>neutralnie, bez efektów.</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>46. Panel: przejscia map</t>
+          <t>46. Panel: przejścia map</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>`Przejścia map`, `Brak jawnych przejść dla tej mapy`</t>
+          <t/>
         </is>
       </c>
       <c r="G263" t="inlineStr">
